--- a/docs/downloads/04/tbl_other_educ_sex_alaotra_tous.xlsx
+++ b/docs/downloads/04/tbl_other_educ_sex_alaotra_tous.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E88"/>
+  <dimension ref="A1:E79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -398,10 +398,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E2">
-        <v>20</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="3">
@@ -463,14 +463,8 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1.5</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -490,10 +484,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E6">
-        <v>44.8</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="7">
@@ -545,24 +539,18 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Alaotra - Ambatoharanana</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="D9">
-        <v>33</v>
-      </c>
-      <c r="E9">
-        <v>26.2</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -578,14 +566,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D10">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="E10">
-        <v>38.1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11">
@@ -601,14 +589,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D11">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="E11">
-        <v>25.4</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="12">
@@ -624,14 +612,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D12">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="E12">
-        <v>8.699999999999999</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="13">
@@ -647,14 +635,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Universitaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D13">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E13">
-        <v>1.6</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="14">
@@ -674,10 +662,10 @@
         </is>
       </c>
       <c r="D14">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E14">
-        <v>36.2</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="15">
@@ -739,37 +727,37 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D17">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E17">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Alaotra - Ambodivoara</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Universitaire</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E18">
-        <v>1.2</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="19">
@@ -785,14 +773,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D19">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="E19">
-        <v>18.4</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="20">
@@ -808,14 +796,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D20">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E20">
-        <v>39.8</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="21">
@@ -831,14 +819,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D21">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="E21">
-        <v>29.6</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="22">
@@ -849,19 +837,19 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D22">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E22">
-        <v>10.2</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="23">
@@ -872,19 +860,19 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Universitaire</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D23">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="24">
@@ -900,14 +888,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D24">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E24">
-        <v>32.4</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="25">
@@ -923,60 +911,60 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D25">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="E25">
-        <v>45.6</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Alaotra - Ambohidrony</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D26">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="E26">
-        <v>17.6</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Alaotra - Ambohidrony</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D27">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="E27">
-        <v>4.4</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="28">
@@ -992,14 +980,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D28">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="E28">
-        <v>32.6</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="29">
@@ -1015,14 +1003,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D29">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="E29">
-        <v>40.7</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="30">
@@ -1033,19 +1021,19 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D30">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E30">
-        <v>19.8</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="31">
@@ -1056,19 +1044,19 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D31">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="E31">
-        <v>3.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32">
@@ -1079,19 +1067,19 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Universitaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D32">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E32">
-        <v>3.5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33">
@@ -1107,106 +1095,106 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D33">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E33">
-        <v>28.3</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Alaotra - Analamiranga</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D34">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E34">
-        <v>50</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Alaotra - Analamiranga</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D35">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="E35">
-        <v>15</v>
+        <v>44</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Alaotra - Analamiranga</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D36">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E36">
-        <v>5</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Alaotra - Analamiranga</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Universitaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D37">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E37">
-        <v>1.7</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="38">
@@ -1217,7 +1205,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1226,10 +1214,10 @@
         </is>
       </c>
       <c r="D38">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E38">
-        <v>27.4</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="39">
@@ -1240,7 +1228,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1249,10 +1237,10 @@
         </is>
       </c>
       <c r="D39">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="E39">
-        <v>44</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="40">
@@ -1263,7 +1251,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1272,10 +1260,10 @@
         </is>
       </c>
       <c r="D40">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E40">
-        <v>23.8</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="41">
@@ -1286,19 +1274,19 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D41">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E41">
-        <v>4.8</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="42">
@@ -1307,108 +1295,102 @@
           <t>Alaotra - Analamiranga</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
       <c r="C42" t="inlineStr">
         <is>
           <t>Inconnu</t>
         </is>
-      </c>
-      <c r="D42">
-        <v>14</v>
-      </c>
-      <c r="E42">
-        <v>27.5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D43">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="E43">
-        <v>47.1</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D44">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="E44">
-        <v>21.6</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D45">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="E45">
-        <v>3.9</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Avaradrano</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D46">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E46">
-        <v>100</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="47">
@@ -1419,7 +1401,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1428,10 +1410,10 @@
         </is>
       </c>
       <c r="D47">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E47">
-        <v>20.5</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="48">
@@ -1442,7 +1424,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1451,10 +1433,10 @@
         </is>
       </c>
       <c r="D48">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="E48">
-        <v>49.4</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="49">
@@ -1465,7 +1447,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1474,10 +1456,10 @@
         </is>
       </c>
       <c r="D49">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="E49">
-        <v>19.9</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="50">
@@ -1488,19 +1470,19 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D50">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E50">
-        <v>9.6</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="51">
@@ -1509,21 +1491,10 @@
           <t>Alaotra - Avaradrano</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Femme</t>
-        </is>
-      </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Universitaire</t>
-        </is>
-      </c>
-      <c r="D51">
-        <v>1</v>
-      </c>
-      <c r="E51">
-        <v>0.6</v>
+          <t>Inconnu</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -1532,126 +1503,125 @@
           <t>Alaotra - Avaradrano</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="D52">
-        <v>33</v>
-      </c>
-      <c r="E52">
-        <v>37.1</v>
+          <t>Primaire</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D53">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="E53">
-        <v>50.6</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D54">
-        <v>9</v>
+        <v>74</v>
       </c>
       <c r="E54">
-        <v>10.1</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D55">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E55">
-        <v>2.2</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Feramanga Atsimo</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D56">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E56">
-        <v>33.3</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Feramanga Atsimo</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D57">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="E57">
-        <v>66.7</v>
+        <v>30.7</v>
       </c>
     </row>
     <row r="58">
@@ -1662,19 +1632,19 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D58">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="E58">
-        <v>22.8</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="59">
@@ -1685,19 +1655,19 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D59">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="E59">
-        <v>54.4</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="60">
@@ -1708,25 +1678,25 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D60">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E60">
-        <v>14.7</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1736,20 +1706,20 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D61">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E61">
-        <v>7.4</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1759,66 +1729,66 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Universitaire</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D62">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="E62">
-        <v>0.7</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D63">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E63">
-        <v>34.2</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D64">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="E64">
-        <v>47.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1828,20 +1798,20 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D65">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E65">
-        <v>12.3</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1851,20 +1821,20 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D66">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="E66">
-        <v>5.3</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1874,14 +1844,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Universitaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D67">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E67">
-        <v>0.9</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="68">
@@ -1892,19 +1862,19 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D68">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="E68">
-        <v>22.2</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="69">
@@ -1913,27 +1883,16 @@
           <t>Alaotra - Mangabe</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Femme</t>
-        </is>
-      </c>
       <c r="C69" t="inlineStr">
         <is>
           <t>Primaire</t>
         </is>
-      </c>
-      <c r="D69">
-        <v>57</v>
-      </c>
-      <c r="E69">
-        <v>45.2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1943,20 +1902,20 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D70">
-        <v>35</v>
+        <v>180</v>
       </c>
       <c r="E70">
-        <v>27.8</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1966,66 +1925,66 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D71">
-        <v>6</v>
+        <v>407</v>
       </c>
       <c r="E71">
-        <v>4.8</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D72">
-        <v>32</v>
+        <v>195</v>
       </c>
       <c r="E72">
-        <v>34</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D73">
-        <v>38</v>
+        <v>95</v>
       </c>
       <c r="E73">
-        <v>40.4</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2035,20 +1994,20 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D74">
-        <v>18</v>
+        <v>174</v>
       </c>
       <c r="E74">
-        <v>19.1</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2058,32 +2017,37 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D75">
-        <v>6</v>
+        <v>267</v>
       </c>
       <c r="E75">
-        <v>6.4</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D76">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="E76">
-        <v>100</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="77">
@@ -2094,19 +2058,19 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D77">
-        <v>206</v>
+        <v>54</v>
       </c>
       <c r="E77">
-        <v>23.5</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -2115,21 +2079,10 @@
           <t>Alaotra - Tous</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Femme</t>
-        </is>
-      </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D78">
-        <v>407</v>
-      </c>
-      <c r="E78">
-        <v>46.4</v>
+          <t>Inconnu</t>
+        </is>
       </c>
     </row>
     <row r="79">
@@ -2138,218 +2091,10 @@
           <t>Alaotra - Tous</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Femme</t>
-        </is>
-      </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
-      </c>
-      <c r="D79">
-        <v>195</v>
-      </c>
-      <c r="E79">
-        <v>22.2</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Femme</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D80">
-        <v>60</v>
-      </c>
-      <c r="E80">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Femme</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Universitaire</t>
-        </is>
-      </c>
-      <c r="D81">
-        <v>9</v>
-      </c>
-      <c r="E81">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="D82">
-        <v>199</v>
-      </c>
-      <c r="E82">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
           <t>Primaire</t>
         </is>
-      </c>
-      <c r="D83">
-        <v>267</v>
-      </c>
-      <c r="E83">
-        <v>45.6</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
-      </c>
-      <c r="D84">
-        <v>90</v>
-      </c>
-      <c r="E84">
-        <v>15.4</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D85">
-        <v>26</v>
-      </c>
-      <c r="E85">
-        <v>4.4</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Universitaire</t>
-        </is>
-      </c>
-      <c r="D86">
-        <v>3</v>
-      </c>
-      <c r="E86">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="D87">
-        <v>2</v>
-      </c>
-      <c r="E87">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D88">
-        <v>3</v>
-      </c>
-      <c r="E88">
-        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/docs/downloads/04/tbl_other_educ_sex_alaotra_tous.xlsx
+++ b/docs/downloads/04/tbl_other_educ_sex_alaotra_tous.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E79"/>
+  <dimension ref="A1:E97"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -397,12 +397,6 @@
           <t>Inconnu</t>
         </is>
       </c>
-      <c r="D2">
-        <v>11</v>
-      </c>
-      <c r="E2">
-        <v>16.9</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -417,14 +411,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="D3">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="E3">
-        <v>61.5</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="4">
@@ -440,14 +434,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D4">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="E4">
-        <v>16.9</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="5">
@@ -463,8 +457,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
-        </is>
+          <t>Secondaire 1er cycle</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>11</v>
+      </c>
+      <c r="E5">
+        <v>16.9</v>
       </c>
     </row>
     <row r="6">
@@ -475,19 +475,13 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>12</v>
-      </c>
-      <c r="E6">
-        <v>41.4</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -503,14 +497,8 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>11</v>
-      </c>
-      <c r="E7">
-        <v>37.9</v>
+          <t>Inconnu</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -526,14 +514,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="D8">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E8">
-        <v>17.2</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="9">
@@ -549,54 +537,54 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
-        </is>
+          <t>Primaire</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>11</v>
+      </c>
+      <c r="E9">
+        <v>37.9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Alaotra - Ambatoharanana</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D10">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="E10">
-        <v>23</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Alaotra - Ambatoharanana</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D11">
-        <v>48</v>
-      </c>
-      <c r="E11">
-        <v>38.1</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -612,14 +600,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D12">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E12">
-        <v>25.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="13">
@@ -635,14 +623,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="D13">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E13">
-        <v>13.5</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="14">
@@ -653,19 +641,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D14">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="E14">
-        <v>32.5</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="15">
@@ -676,19 +664,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D15">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E15">
-        <v>42.5</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="16">
@@ -699,19 +687,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D16">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E16">
-        <v>15</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="17">
@@ -727,48 +715,48 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D17">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E17">
-        <v>10</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Alaotra - Ambatomanga</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="D18">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E18">
-        <v>16.3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Alaotra - Ambatomanga</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -777,21 +765,21 @@
         </is>
       </c>
       <c r="D19">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E19">
-        <v>39.8</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Alaotra - Ambatomanga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -800,21 +788,21 @@
         </is>
       </c>
       <c r="D20">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="E20">
-        <v>29.6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Alaotra - Ambatomanga</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -823,10 +811,10 @@
         </is>
       </c>
       <c r="D21">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E21">
-        <v>14.3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
@@ -837,19 +825,13 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
           <t>Inconnu</t>
         </is>
-      </c>
-      <c r="D22">
-        <v>19</v>
-      </c>
-      <c r="E22">
-        <v>27.9</v>
       </c>
     </row>
     <row r="23">
@@ -860,19 +842,19 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="D23">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="E23">
-        <v>45.6</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="24">
@@ -883,19 +865,19 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D24">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="E24">
-        <v>17.6</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="25">
@@ -906,25 +888,25 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D25">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="E25">
-        <v>8.800000000000001</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Alaotra - Ambodivoara</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -934,89 +916,83 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D26">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="E26">
-        <v>31.4</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Alaotra - Ambodivoara</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D27">
-        <v>35</v>
-      </c>
-      <c r="E27">
-        <v>40.7</v>
+          <t>Inconnu</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Alaotra - Ambodivoara</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="D28">
         <v>17</v>
       </c>
       <c r="E28">
-        <v>19.8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Alaotra - Ambodivoara</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D29">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="E29">
-        <v>8.1</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Alaotra - Ambodivoara</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1026,20 +1002,20 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D30">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E30">
-        <v>23.3</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Alaotra - Ambodivoara</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1049,14 +1025,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D31">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="E31">
-        <v>50</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -1067,19 +1043,19 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D32">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E32">
-        <v>15</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="33">
@@ -1090,25 +1066,25 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="D33">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E33">
-        <v>11.7</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Ambohidrony</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1118,20 +1094,20 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D34">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="E34">
-        <v>17.9</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Ambohidrony</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1141,20 +1117,20 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D35">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="E35">
-        <v>44</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Ambohidrony</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1164,43 +1140,37 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D36">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E36">
-        <v>23.8</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Ambohidrony</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
-        </is>
-      </c>
-      <c r="D37">
-        <v>12</v>
-      </c>
-      <c r="E37">
-        <v>14.3</v>
+          <t>Inconnu</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Ambohidrony</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1210,20 +1180,20 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="D38">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E38">
-        <v>21.6</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Ambohidrony</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1237,16 +1207,16 @@
         </is>
       </c>
       <c r="D39">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E39">
-        <v>47.1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Ambohidrony</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1260,16 +1230,16 @@
         </is>
       </c>
       <c r="D40">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E40">
-        <v>21.6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Ambohidrony</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1283,10 +1253,10 @@
         </is>
       </c>
       <c r="D41">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E41">
-        <v>9.800000000000001</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="42">
@@ -1295,6 +1265,11 @@
           <t>Alaotra - Analamiranga</t>
         </is>
       </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Femme</t>
+        </is>
+      </c>
       <c r="C42" t="inlineStr">
         <is>
           <t>Inconnu</t>
@@ -1304,7 +1279,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Analamiranga</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1314,20 +1289,20 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="D43">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="E43">
-        <v>19.9</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Analamiranga</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1341,16 +1316,16 @@
         </is>
       </c>
       <c r="D44">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="E44">
-        <v>49.4</v>
+        <v>44</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Analamiranga</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1364,16 +1339,16 @@
         </is>
       </c>
       <c r="D45">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="E45">
-        <v>19.9</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Analamiranga</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1387,16 +1362,16 @@
         </is>
       </c>
       <c r="D46">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E46">
-        <v>10.9</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Analamiranga</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1408,18 +1383,12 @@
         <is>
           <t>Inconnu</t>
         </is>
-      </c>
-      <c r="D47">
-        <v>29</v>
-      </c>
-      <c r="E47">
-        <v>32.6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Analamiranga</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1429,20 +1398,20 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="D48">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="E48">
-        <v>50.6</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Analamiranga</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1452,20 +1421,20 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D49">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E49">
-        <v>10.1</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Analamiranga</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,44 +1444,55 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D50">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E50">
-        <v>6.7</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Analamiranga</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
+      </c>
+      <c r="D51">
+        <v>5</v>
+      </c>
+      <c r="E51">
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Analamiranga</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1526,16 +1506,16 @@
         </is>
       </c>
       <c r="D53">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="E53">
-        <v>19.1</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1545,20 +1525,20 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="D54">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="E54">
-        <v>54.4</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1568,20 +1548,20 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D55">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="E55">
-        <v>14.7</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1591,43 +1571,43 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D56">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="E56">
-        <v>11.8</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D57">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="E57">
-        <v>30.7</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1637,20 +1617,20 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D58">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="E58">
-        <v>47.4</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1660,20 +1640,20 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="D59">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E59">
-        <v>12.3</v>
+        <v>27</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1683,117 +1663,95 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D60">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="E60">
-        <v>9.6</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D61">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="E61">
-        <v>19.8</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D62">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="E62">
-        <v>45.2</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Femme</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
-      </c>
-      <c r="D63">
-        <v>35</v>
-      </c>
-      <c r="E63">
-        <v>27.8</v>
+          <t>Non scolarisé</t>
+        </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Femme</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
-        </is>
-      </c>
-      <c r="D64">
-        <v>9</v>
-      </c>
-      <c r="E64">
-        <v>7.1</v>
+          <t>Primaire</t>
+        </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1802,102 +1760,113 @@
         </is>
       </c>
       <c r="D65">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="E65">
-        <v>29.8</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="D66">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="E66">
-        <v>40.4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D67">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="E67">
-        <v>19.1</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D68">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E68">
-        <v>10.6</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Feramanga Atsimo</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
+      </c>
+      <c r="D69">
+        <v>16</v>
+      </c>
+      <c r="E69">
+        <v>11.8</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1906,85 +1875,85 @@
         </is>
       </c>
       <c r="D70">
-        <v>180</v>
+        <v>9</v>
       </c>
       <c r="E70">
-        <v>20.5</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="D71">
-        <v>407</v>
+        <v>26</v>
       </c>
       <c r="E71">
-        <v>46.4</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D72">
-        <v>195</v>
+        <v>54</v>
       </c>
       <c r="E72">
-        <v>22.2</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D73">
-        <v>95</v>
+        <v>14</v>
       </c>
       <c r="E73">
-        <v>10.8</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1994,104 +1963,507 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D74">
-        <v>174</v>
+        <v>11</v>
       </c>
       <c r="E74">
-        <v>29.7</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D75">
-        <v>267</v>
+        <v>9</v>
       </c>
       <c r="E75">
-        <v>45.6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="D76">
-        <v>90</v>
+        <v>16</v>
       </c>
       <c r="E76">
-        <v>15.4</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D77">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E77">
-        <v>9.199999999999999</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Alaotra - Mangabe</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
+          <t>Secondaire 1er cycle</t>
+        </is>
+      </c>
+      <c r="D78">
+        <v>35</v>
+      </c>
+      <c r="E78">
+        <v>27.8</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>Alaotra - Mangabe</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Femme</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
+      </c>
+      <c r="D79">
+        <v>9</v>
+      </c>
+      <c r="E79">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Alaotra - Mangabe</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Inconnu</t>
+        </is>
+      </c>
+      <c r="D80">
+        <v>8</v>
+      </c>
+      <c r="E80">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Alaotra - Mangabe</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Non scolarisé</t>
+        </is>
+      </c>
+      <c r="D81">
+        <v>20</v>
+      </c>
+      <c r="E81">
+        <v>21.3</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Alaotra - Mangabe</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Primaire</t>
+        </is>
+      </c>
+      <c r="D82">
+        <v>38</v>
+      </c>
+      <c r="E82">
+        <v>40.4</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Alaotra - Mangabe</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Secondaire 1er cycle</t>
+        </is>
+      </c>
+      <c r="D83">
+        <v>18</v>
+      </c>
+      <c r="E83">
+        <v>19.1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Alaotra - Mangabe</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
+      </c>
+      <c r="D84">
+        <v>10</v>
+      </c>
+      <c r="E84">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Alaotra - Mangabe</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Primaire</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
           <t>Alaotra - Tous</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Femme</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Inconnu</t>
+        </is>
+      </c>
+      <c r="D86">
+        <v>47</v>
+      </c>
+      <c r="E86">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Femme</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Non scolarisé</t>
+        </is>
+      </c>
+      <c r="D87">
+        <v>133</v>
+      </c>
+      <c r="E87">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Femme</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Primaire</t>
+        </is>
+      </c>
+      <c r="D88">
+        <v>407</v>
+      </c>
+      <c r="E88">
+        <v>46.4</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Femme</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Secondaire 1er cycle</t>
+        </is>
+      </c>
+      <c r="D89">
+        <v>195</v>
+      </c>
+      <c r="E89">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Femme</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
+      </c>
+      <c r="D90">
+        <v>95</v>
+      </c>
+      <c r="E90">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Inconnu</t>
+        </is>
+      </c>
+      <c r="D91">
+        <v>38</v>
+      </c>
+      <c r="E91">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Non scolarisé</t>
+        </is>
+      </c>
+      <c r="D92">
+        <v>136</v>
+      </c>
+      <c r="E92">
+        <v>23.2</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Primaire</t>
+        </is>
+      </c>
+      <c r="D93">
+        <v>267</v>
+      </c>
+      <c r="E93">
+        <v>45.6</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Secondaire 1er cycle</t>
+        </is>
+      </c>
+      <c r="D94">
+        <v>90</v>
+      </c>
+      <c r="E94">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
+      </c>
+      <c r="D95">
+        <v>54</v>
+      </c>
+      <c r="E95">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Non scolarisé</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
         <is>
           <t>Primaire</t>
         </is>

--- a/docs/downloads/04/tbl_other_educ_sex_alaotra_tous.xlsx
+++ b/docs/downloads/04/tbl_other_educ_sex_alaotra_tous.xlsx
@@ -384,7 +384,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -401,7 +401,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -424,7 +424,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -447,7 +447,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -470,7 +470,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -487,7 +487,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -504,7 +504,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -527,7 +527,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -573,7 +573,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -590,7 +590,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -636,7 +636,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -682,7 +682,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -705,7 +705,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -728,7 +728,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -751,7 +751,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -774,7 +774,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -797,7 +797,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -820,7 +820,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -837,7 +837,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -860,7 +860,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -883,7 +883,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -906,7 +906,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -929,7 +929,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -969,7 +969,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -992,7 +992,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1015,7 +1015,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1038,7 +1038,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1061,7 +1061,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1084,7 +1084,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1107,7 +1107,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1130,7 +1130,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1153,7 +1153,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1170,7 +1170,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1193,7 +1193,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1216,7 +1216,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1239,7 +1239,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1262,7 +1262,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1279,7 +1279,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1302,7 +1302,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1325,7 +1325,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1348,7 +1348,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1371,7 +1371,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1388,7 +1388,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1411,7 +1411,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1434,7 +1434,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1457,7 +1457,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1480,7 +1480,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1492,7 +1492,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1515,7 +1515,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1538,7 +1538,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1561,7 +1561,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1584,7 +1584,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1607,7 +1607,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1630,7 +1630,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1653,7 +1653,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1676,7 +1676,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1699,7 +1699,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1722,7 +1722,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1734,7 +1734,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1746,7 +1746,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1769,7 +1769,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1792,7 +1792,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1815,7 +1815,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1838,7 +1838,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1861,7 +1861,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1884,7 +1884,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1907,7 +1907,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1930,7 +1930,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1953,7 +1953,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1976,7 +1976,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1999,7 +1999,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2022,7 +2022,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2068,7 +2068,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2091,7 +2091,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2114,7 +2114,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2137,7 +2137,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2160,7 +2160,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2183,7 +2183,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2206,7 +2206,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2218,7 +2218,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2241,7 +2241,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2264,7 +2264,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2287,7 +2287,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2310,7 +2310,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2333,7 +2333,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2356,7 +2356,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2379,7 +2379,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2402,7 +2402,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2448,7 +2448,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2460,7 +2460,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
